--- a/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAFF428-C9AC-914F-863D-9BD6A252415B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B204D184-BB88-8949-A6BF-04D5F4F4AC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3400" yWindow="740" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32460" yWindow="-22480" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -359,12 +359,6 @@
     <t>optional</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
-    <t>https://chumbausa.com/yaupon-steel-mountain-bike-29er-27plus?gad_source=1&amp;gad_campaignid=22037681435&amp;gbraid=0AAAAACx2TJJof_f7wQBU7W9AxJ9w9Uvlo&amp;gclid=Cj0KCQjw-ZHEBhCxARIsAGGN96Jx8h9S-QSPWTdrYS_K7zHvmR9KCc-WPR4MAJ4QSBs-z1QGdI0NbgIaAhOTEALw_wcB</t>
-  </si>
-  <si>
     <t>1106-1126</t>
   </si>
   <si>
@@ -408,6 +402,12 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://chumbausa.com/yaupon-mtb-bar</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -781,7 +781,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -1435,22 +1435,22 @@
         <v>24</v>
       </c>
       <c r="K19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="N19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="O19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.3">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>30</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>88</v>
@@ -1830,18 +1830,18 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -1896,8 +1896,8 @@
       <c r="A43" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>80</v>
+      <c r="B43" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -2085,7 +2085,7 @@
         <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B204D184-BB88-8949-A6BF-04D5F4F4AC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5947F0-0ECD-5741-B80A-703CB391F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32460" yWindow="-22480" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7920" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -404,10 +404,13 @@
     <t>suspension</t>
   </si>
   <si>
-    <t>https://chumbausa.com/yaupon-mtb-bar</t>
-  </si>
-  <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://chumbausa.com/yaupon-steel-mountain-bike-29er-27plus</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/eba7bd27-f856-4e50-869a-9af459046fc1/2024-MADE-BIke-Show-Chumba-Cycles-Yaupon-Drop-Bar-Hardtail-1-%281%29.jpg?format=2500w</t>
   </si>
 </sst>
 </file>
@@ -805,7 +808,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -2085,7 +2093,7 @@
         <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5947F0-0ECD-5741-B80A-703CB391F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C48C8B3-1E3F-CB41-8FFA-6CB0D5068817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/eba7bd27-f856-4e50-869a-9af459046fc1/2024-MADE-BIke-Show-Chumba-Cycles-Yaupon-Drop-Bar-Hardtail-1-%281%29.jpg?format=2500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri, USA</t>
   </si>
 </sst>
 </file>
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2096,6 +2102,14 @@
         <v>123</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C48C8B3-1E3F-CB41-8FFA-6CB0D5068817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641AAFCC-0F06-974A-A3F5-45F985251B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -417,6 +417,24 @@
   </si>
   <si>
     <t>Kansas City, Missouri, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -771,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1942,171 +1960,201 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>58</v>
       </c>
-      <c r="B50">
+      <c r="B56">
         <v>31.6</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>60</v>
       </c>
-      <c r="B52">
+      <c r="B58">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>69</v>
       </c>
-      <c r="B61">
+      <c r="B67">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>70</v>
       </c>
-      <c r="B62">
+      <c r="B68">
         <v>1</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>76</v>
       </c>
-      <c r="B68">
+      <c r="B74">
         <v>1695</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>126</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>127</v>
       </c>
     </row>

--- a/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
+++ b/data/gravel/Chumba Yaupon Steel Suspension 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641AAFCC-0F06-974A-A3F5-45F985251B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9736D89-ED6F-5C47-8EAC-99520B2BA073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9380" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -380,9 +380,6 @@
     <t>trail</t>
   </si>
   <si>
-    <t>a8:h31</t>
-  </si>
-  <si>
     <t>Yaupon Steel Suspension</t>
   </si>
   <si>
@@ -435,6 +432,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:h33</t>
   </si>
 </sst>
 </file>
@@ -789,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -808,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -832,12 +838,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -845,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -1016,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C19" si="3">K14</f>
+        <f t="shared" ref="C11:C18" si="3">K14</f>
         <v>95</v>
       </c>
       <c r="D11">
@@ -1391,23 +1397,23 @@
         <v>391</v>
       </c>
       <c r="D18">
-        <f t="shared" ref="D18:D19" si="13">L21</f>
+        <f t="shared" ref="D18" si="13">L21</f>
         <v>406</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18:E19" si="14">M21</f>
+        <f t="shared" ref="E18" si="14">M21</f>
         <v>414</v>
       </c>
       <c r="F18">
-        <f t="shared" ref="F18:F19" si="15">N21</f>
+        <f t="shared" ref="F18" si="15">N21</f>
         <v>423</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18:G19" si="16">O21</f>
+        <f t="shared" ref="G18" si="16">O21</f>
         <v>431</v>
       </c>
       <c r="H18">
-        <f t="shared" ref="H18:H19" si="17">P21</f>
+        <f t="shared" ref="H18" si="17">P21</f>
         <v>438</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -1440,27 +1446,27 @@
         <v>30</v>
       </c>
       <c r="C19">
-        <f t="shared" si="3"/>
+        <f>K24</f>
         <v>632</v>
       </c>
       <c r="D19">
-        <f t="shared" si="13"/>
+        <f>L24</f>
         <v>646</v>
       </c>
       <c r="E19">
-        <f t="shared" si="14"/>
+        <f>M24</f>
         <v>651</v>
       </c>
       <c r="F19">
-        <f t="shared" si="15"/>
+        <f>N24</f>
         <v>656</v>
       </c>
       <c r="G19">
-        <f t="shared" si="16"/>
+        <f>O24</f>
         <v>665</v>
       </c>
       <c r="H19">
-        <f t="shared" si="17"/>
+        <f>P24</f>
         <v>674</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -1581,581 +1587,623 @@
     </row>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22">
+        <v>120</v>
+      </c>
+      <c r="D22">
+        <v>120</v>
+      </c>
+      <c r="E22">
+        <v>120</v>
+      </c>
+      <c r="F22">
+        <v>120</v>
+      </c>
+      <c r="G22">
+        <v>120</v>
+      </c>
+      <c r="H22">
+        <v>120</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="1:16" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="1:16" ht="21" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K24" s="3">
         <v>632</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L24" s="3">
         <v>646</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M24" s="3">
         <v>651</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N24" s="3">
         <v>656</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O24" s="3">
         <v>665</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P24" s="3">
         <v>674</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25">
-        <v>50</v>
-      </c>
-      <c r="D25">
-        <v>50</v>
-      </c>
-      <c r="E25">
-        <v>50</v>
-      </c>
-      <c r="F25">
-        <v>50</v>
-      </c>
-      <c r="G25">
-        <v>60</v>
-      </c>
-      <c r="H25">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="H27">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28">
-        <v>57</v>
-      </c>
-      <c r="D28">
-        <v>57</v>
-      </c>
-      <c r="E28">
-        <v>57</v>
-      </c>
-      <c r="F28">
-        <v>57</v>
-      </c>
-      <c r="G28">
-        <v>57</v>
-      </c>
-      <c r="H28">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D29">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="G29">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="H29">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>57</v>
+      </c>
+      <c r="D30">
+        <v>57</v>
+      </c>
+      <c r="E30">
+        <v>57</v>
+      </c>
+      <c r="F30">
+        <v>57</v>
+      </c>
+      <c r="G30">
+        <v>57</v>
+      </c>
+      <c r="H30">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <v>61</v>
+      </c>
+      <c r="D31">
+        <v>61</v>
+      </c>
+      <c r="E31">
+        <v>61</v>
+      </c>
+      <c r="F31">
+        <v>61</v>
+      </c>
+      <c r="G31">
+        <v>61</v>
+      </c>
+      <c r="H31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="C30">
-        <f>ROUND(C32*2.54,1)</f>
+      <c r="C32">
+        <f>ROUND(C34*2.54,1)</f>
         <v>152.4</v>
       </c>
-      <c r="D30">
-        <f>ROUND(AVERAGE(D32,C33)*2.54, 1)</f>
+      <c r="D32">
+        <f>ROUND(AVERAGE(D34,C35)*2.54, 1)</f>
         <v>168.9</v>
       </c>
-      <c r="E30">
-        <f t="shared" ref="E30:H30" si="18">ROUND(AVERAGE(E32,D33)*2.54, 1)</f>
+      <c r="E32">
+        <f t="shared" ref="E32:H32" si="18">ROUND(AVERAGE(E34,D35)*2.54, 1)</f>
         <v>175.3</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="18"/>
         <v>179.1</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <f t="shared" si="18"/>
         <v>185.4</v>
       </c>
-      <c r="H30">
+      <c r="H32">
         <f t="shared" si="18"/>
         <v>188</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="C31">
-        <f>D30</f>
+      <c r="C33">
+        <f>D32</f>
         <v>168.9</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:G31" si="19">E30</f>
+      <c r="D33">
+        <f t="shared" ref="D33:G33" si="19">E32</f>
         <v>175.3</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="19"/>
         <v>179.1</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="19"/>
         <v>185.4</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <f t="shared" si="19"/>
         <v>188</v>
       </c>
-      <c r="H31">
-        <f t="shared" ref="H31" si="20">ROUND(H33*2.54,1)</f>
+      <c r="H33">
+        <f t="shared" ref="H33" si="20">ROUND(H35*2.54,1)</f>
         <v>198.1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C32">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C34">
         <v>60</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>67</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>69</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <v>71</v>
       </c>
-      <c r="G32">
+      <c r="G34">
         <v>73</v>
       </c>
-      <c r="H32">
+      <c r="H34">
         <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33">
-        <v>66</v>
-      </c>
-      <c r="D33">
-        <v>69</v>
-      </c>
-      <c r="E33">
-        <v>70</v>
-      </c>
-      <c r="F33">
-        <v>73</v>
-      </c>
-      <c r="G33">
-        <v>74</v>
-      </c>
-      <c r="H33">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>66</v>
+      </c>
+      <c r="D35">
+        <v>69</v>
+      </c>
+      <c r="E35">
+        <v>70</v>
+      </c>
+      <c r="F35">
+        <v>73</v>
+      </c>
+      <c r="G35">
+        <v>74</v>
+      </c>
+      <c r="H35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>80</v>
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>2.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1">
-        <v>120</v>
+        <v>49</v>
+      </c>
+      <c r="B43">
+        <v>2.8</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B44">
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B45" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>54</v>
+      </c>
+      <c r="B48">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>55</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56">
-        <v>31.6</v>
+        <v>56</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B58">
-        <v>38</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>70</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>107</v>
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B74">
-        <v>1695</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>78</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="B76">
+        <v>1695</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>79</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80" t="s">
         <v>126</v>
-      </c>
-      <c r="B78" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
